--- a/artfynd/A 42291-2022 artfynd.xlsx
+++ b/artfynd/A 42291-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 42291-2022 artfynd.xlsx
+++ b/artfynd/A 42291-2022 artfynd.xlsx
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>17270638</v>
+        <v>17270621</v>
       </c>
       <c r="B2" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -719,10 +714,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>567548.460485698</v>
+        <v>567548</v>
       </c>
       <c r="R2" t="n">
-        <v>6973706.54719912</v>
+        <v>6973707</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -752,19 +747,9 @@
           <t>2014-07-04</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2014-07-04</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -800,15 +785,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>17270621</v>
+        <v>17270638</v>
       </c>
       <c r="B3" t="n">
-        <v>77506</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -816,21 +796,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -844,10 +824,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>567548.460485698</v>
+        <v>567548</v>
       </c>
       <c r="R3" t="n">
-        <v>6973706.54719912</v>
+        <v>6973707</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -877,19 +857,9 @@
           <t>2014-07-04</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2014-07-04</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 42291-2022 artfynd.xlsx
+++ b/artfynd/A 42291-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -782,6 +787,11 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17270621</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -892,8 +902,17 @@
           <t>SCA Skog Naturvärdesinventering</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17270638</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>